--- a/modules/maxdiff/templates/maxdiff_config_template.xlsx
+++ b/modules/maxdiff/templates/maxdiff_config_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t xml:space="preserve">Topic</t>
   </si>
@@ -251,10 +251,34 @@
     <t xml:space="preserve">12345, 42, 98765</t>
   </si>
   <si>
+    <t xml:space="preserve">Brand_Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1e3a5f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary brand colour for HTML report and simulator (hex format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1e3a5f, #2c3e50, #003366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accent_Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2aa198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary accent colour for HTML report (hex format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2aa198, #e67e22, #27ae60</t>
+  </si>
+  <si>
     <t xml:space="preserve">Module_Version</t>
   </si>
   <si>
-    <t xml:space="preserve">v10.0</t>
+    <t xml:space="preserve">v11.0</t>
   </si>
   <si>
     <t xml:space="preserve">Module version (for tracking)</t>
@@ -596,6 +620,15 @@
     <t xml:space="preserve">Worst_Value_Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Anchor_Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column containing anchor/must-have selections (comma-separated Item_IDs or blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MustHave_Items, Anchor_Q (e.g. 'ITEM_01,ITEM_03,ITEM_05')</t>
+  </si>
+  <si>
     <t xml:space="preserve">Note</t>
   </si>
   <si>
@@ -725,7 +758,88 @@
     <t xml:space="preserve">Generate_Charts</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate visualization charts</t>
+    <t xml:space="preserve">Generate PNG/PDF visualization charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_HTML_Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate interactive HTML report with SVG charts and tabbed layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (produces self-contained .html file)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Simulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate interactive HTML simulator (head-to-head, portfolio builder)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (requires HB or logit results)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_TURF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run TURF (Total Unduplicated Reach &amp; Frequency) portfolio optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (requires individual-level utilities from HB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURF_Max_Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum portfolio size for TURF analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to n_items (default: min(10, n_items))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURF_Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method for classifying items as appealing in TURF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO | TOP_3 | ABOVE_MEAN | ABOVE_ZERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has_Anchor_Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the survey includes an anchor/must-have question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor_Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportion threshold for classifying items as must-have (0.0-1.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0-1.0 (items with anchor rate above this = must-have)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score_Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to display preference scores in reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTILITY | PREFERENCE_SHARE | BOTH</t>
   </si>
   <si>
     <t xml:space="preserve">Utility_Scale</t>
@@ -1749,7 +1863,41 @@
         <v>79</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1774,36 +1922,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>1</v>
@@ -1820,13 +1968,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>1</v>
@@ -1843,13 +1991,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>1</v>
@@ -1866,13 +2014,13 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>1</v>
@@ -1889,13 +2037,13 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
@@ -1912,13 +2060,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
@@ -1935,13 +2083,13 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1</v>
@@ -1958,13 +2106,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1</v>
@@ -1981,13 +2129,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>1</v>
@@ -2004,13 +2152,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1</v>
@@ -2027,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>36</v>
@@ -2038,79 +2186,79 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2282,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2146,55 +2294,55 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>60</v>
@@ -2203,38 +2351,38 @@
         <v>56</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>40</v>
@@ -2243,38 +2391,38 @@
         <v>56</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>40</v>
@@ -2283,10 +2431,10 @@
         <v>56</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>40</v>
@@ -2294,7 +2442,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>40</v>
@@ -2303,10 +2451,10 @@
         <v>56</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>40</v>
@@ -2314,7 +2462,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>40</v>
@@ -2323,10 +2471,10 @@
         <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>40</v>
@@ -2334,42 +2482,42 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2392,7 +2540,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2404,134 +2552,151 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -2541,17 +2706,17 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2575,33 +2740,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>60</v>
@@ -2615,16 +2780,16 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1</v>
@@ -2635,13 +2800,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>60</v>
@@ -2655,16 +2820,16 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1</v>
@@ -2675,16 +2840,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
@@ -2695,16 +2860,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1</v>
@@ -2715,16 +2880,16 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>1</v>
@@ -2735,16 +2900,16 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1</v>
@@ -2755,16 +2920,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>1</v>
@@ -2775,7 +2940,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>36</v>
@@ -2786,68 +2951,68 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2878,175 +3043,287 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>145</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>253</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>255</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/modules/maxdiff/templates/maxdiff_config_template.xlsx
+++ b/modules/maxdiff/templates/maxdiff_config_template.xlsx
@@ -13,12 +13,16 @@
     <sheet name="SURVEY_MAPPING" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="SEGMENT_SETTINGS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="OUTPUT_SETTINGS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="REPORT_SETTINGS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SLIDES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IMAGES" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="STUDY_IDENTIFICATION" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
   <si>
     <t xml:space="preserve">Topic</t>
   </si>
@@ -65,6 +69,15 @@
     <t xml:space="preserve">OUTPUT_SETTINGS: Control what outputs are generated - Optional (has defaults)</t>
   </si>
   <si>
+    <t xml:space="preserve">REPORT_SETTINGS: Branding, logos, and report generation options - Optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLIDES: Custom report pages inserted before/after diagnostics - Optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMAGES: Embedded images for specific report panels - Optional</t>
+  </si>
+  <si>
     <t xml:space="preserve">WORKFLOW: DESIGN MODE</t>
   </si>
   <si>
@@ -722,6 +735,9 @@
     <t xml:space="preserve">Order for display within the segment group</t>
   </si>
   <si>
+    <t xml:space="preserve">--- OUTPUT FORMATS ---</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generate_Design_File</t>
   </si>
   <si>
@@ -779,6 +795,15 @@
     <t xml:space="preserve">YES or NO (requires HB or logit results)</t>
   </si>
   <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- TURF ANALYSIS ---</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generate_TURF</t>
   </si>
   <si>
@@ -803,13 +828,16 @@
     <t xml:space="preserve">TURF_Threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO</t>
+    <t xml:space="preserve">ABOVE_MEAN</t>
   </si>
   <si>
     <t xml:space="preserve">Method for classifying items as appealing in TURF</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO | TOP_3 | ABOVE_MEAN | ABOVE_ZERO</t>
+    <t xml:space="preserve">ABOVE_MEAN | TOP_3 | TOP_K | ABOVE_ZERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- ANCHORED MAXDIFF ---</t>
   </si>
   <si>
     <t xml:space="preserve">Has_Anchor_Question</t>
@@ -818,6 +846,12 @@
     <t xml:space="preserve">Whether the survey includes an anchor/must-have question</t>
   </si>
   <si>
+    <t xml:space="preserve">Column name containing anchor responses (leave blank if Has_Anchor_Question = NO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column name from data file</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anchor_Threshold</t>
   </si>
   <si>
@@ -830,6 +864,21 @@
     <t xml:space="preserve">0.0-1.0 (items with anchor rate above this = must-have)</t>
   </si>
   <si>
+    <t xml:space="preserve">Anchor_Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMA_SEPARATED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format of anchor variable data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMA_SEPARATED | BINARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- DISPLAY &amp; FORMATTING ---</t>
+  </si>
+  <si>
     <t xml:space="preserve">Score_Display</t>
   </si>
   <si>
@@ -900,6 +949,138 @@
   </si>
   <si>
     <t xml:space="preserve">300-1200 (pixels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#323367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary brand colour for report theme (hex format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#323367, #1e3a5f, #2c3e50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#CC9900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accent colour for highlights and secondary elements (hex format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#CC9900, #e67e22, #27ae60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Researcher_Logo_Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File path to researcher/agency logo image (PNG/JPG, leave blank for none)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logos/agency_logo.png, C:/Logos/company.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client_Logo_Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File path to client logo image (PNG/JPG, leave blank for none)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logos/client_logo.png, C:/Logos/client_brand.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report_Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom report title (leave blank to use Project_Name from PROJECT_SETTINGS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Preference MaxDiff Study Q1 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include_Methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include a methodology section in the HTML report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image_Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About This Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;This MaxDiff study was conducted to understand customer preferences across key product attributes.&lt;/p&gt;&lt;p&gt;Results are based on a sample of N=500 respondents.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEFORE_DIAGNOSTICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide title displayed as a heading in the report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTML content for the slide body (supports &lt;p&gt;, &lt;ul&gt;, &lt;li&gt;, &lt;b&gt;, &lt;em&gt; tags)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to insert the slide in the report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional file path to an image displayed on the slide (PNG/JPG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images/study_overview.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1: Study overview and key findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which report panel to embed the image in: summary, preferences, items, turf, segments, diagnostics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File path to the image file (PNG/JPG, relative to config or absolute)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional caption text displayed below the image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Preference Study Q1 2026, Product Features MaxDiff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jane Smith, John Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Research LampPost, Acme Research Partners</t>
   </si>
 </sst>
 </file>
@@ -957,12 +1138,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6D28D9"/>
+        <fgColor rgb="FF323367"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F3FF"/>
+        <fgColor rgb="FFE8E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -982,7 +1163,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8B5CF6"/>
+        <fgColor rgb="FFCC9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -996,30 +1177,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF4C1D95"/>
+        <color rgb="FF1A1A4E"/>
       </left>
       <right style="thin">
-        <color rgb="FF4C1D95"/>
+        <color rgb="FF1A1A4E"/>
       </right>
       <top style="thin">
-        <color rgb="FF4C1D95"/>
+        <color rgb="FF1A1A4E"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF4C1D95"/>
+        <color rgb="FF1A1A4E"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE9D5FF"/>
+        <color rgb="FFC8C8D8"/>
       </left>
       <right style="thin">
-        <color rgb="FFE9D5FF"/>
+        <color rgb="FFC8C8D8"/>
       </right>
       <top style="thin">
-        <color rgb="FFE9D5FF"/>
+        <color rgb="FFC8C8D8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE9D5FF"/>
+        <color rgb="FFC8C8D8"/>
       </bottom>
     </border>
     <border>
@@ -1397,10 +1578,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1489,12 +1670,12 @@
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1513,12 +1694,12 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
@@ -1529,12 +1710,12 @@
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>21</v>
@@ -1553,12 +1734,12 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>24</v>
@@ -1585,12 +1766,12 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>28</v>
@@ -1609,12 +1790,12 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>31</v>
@@ -1637,11 +1818,215 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
+      <c r="A32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="50.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="50.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'summary,preferences,items,turf,segments,diagnostics'</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A20</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="75.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -1664,245 +2049,257 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'DESIGN,ANALYSIS'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1922,36 +2319,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>1</v>
@@ -1968,13 +2365,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>1</v>
@@ -1991,13 +2388,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>1</v>
@@ -2014,13 +2411,13 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>1</v>
@@ -2037,13 +2434,13 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
@@ -2060,13 +2457,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
@@ -2083,13 +2480,13 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1</v>
@@ -2106,13 +2503,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1</v>
@@ -2129,13 +2526,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>1</v>
@@ -2152,13 +2549,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1</v>
@@ -2175,10 +2572,10 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1</v>
@@ -2186,79 +2583,79 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2282,247 +2679,283 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'BALANCED,OPTIMAL,RANDOM'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B8:B8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B9:B9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B10:B10</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2540,163 +2973,163 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2706,17 +3139,17 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2740,36 +3173,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>1</v>
@@ -2780,16 +3213,16 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1</v>
@@ -2800,16 +3233,16 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>1</v>
@@ -2820,16 +3253,16 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1</v>
@@ -2840,16 +3273,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
@@ -2860,16 +3293,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1</v>
@@ -2880,16 +3313,16 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>1</v>
@@ -2900,16 +3333,16 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>223</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1</v>
@@ -2920,16 +3353,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>1</v>
@@ -2940,10 +3373,10 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1</v>
@@ -2951,68 +3384,68 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3027,307 +3460,762 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="28.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="50.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>153</v>
+      <c r="A2" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>242</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>249</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>258</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>263</v>
+      <c r="B12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="4" t="s">
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>277</v>
+      <c r="B16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D20" s="4" t="s">
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D21" s="4" t="s">
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
         <v>293</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4:B4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B7:B7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B8:B8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B9:B9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B10:B10</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B11:B11</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B13:B13</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B17:B17</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B24:B24</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B25:B25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'ABOVE_MEAN,TOP_3,TOP_K,ABOVE_ZERO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B15:B15</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'COMMA_SEPARATED,BINARY'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B20:B20</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="60.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'YES,NO'</xm:f>
+          </x14:formula1>
+          <xm:sqref>B7:B7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="40.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'BEFORE_DIAGNOSTICS,AFTER_DIAGNOSTICS'</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C20</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/modules/maxdiff/templates/maxdiff_config_template.xlsx
+++ b/modules/maxdiff/templates/maxdiff_config_template.xlsx
@@ -13,16 +13,13 @@
     <sheet name="SURVEY_MAPPING" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="SEGMENT_SETTINGS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="OUTPUT_SETTINGS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="REPORT_SETTINGS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SLIDES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="IMAGES" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="STUDY_IDENTIFICATION" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SLIDES" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
   <si>
     <t xml:space="preserve">Topic</t>
   </si>
@@ -69,15 +66,9 @@
     <t xml:space="preserve">OUTPUT_SETTINGS: Control what outputs are generated - Optional (has defaults)</t>
   </si>
   <si>
-    <t xml:space="preserve">REPORT_SETTINGS: Branding, logos, and report generation options - Optional</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLIDES: Custom report pages inserted before/after diagnostics - Optional</t>
   </si>
   <si>
-    <t xml:space="preserve">IMAGES: Embedded images for specific report panels - Optional</t>
-  </si>
-  <si>
     <t xml:space="preserve">WORKFLOW: DESIGN MODE</t>
   </si>
   <si>
@@ -252,6 +243,18 @@
     <t xml:space="preserve">Region == 'North', Age &gt;= 18 &amp; Age &lt;= 65, Complete == 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Choice_Value_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How best/worst cells are coded: ITEM_ID (Item_ID strings) or ITEM_POSITION (1-based position within the task - how Sawtooth/Alchemer usually export)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM_ID or ITEM_POSITION</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seed</t>
   </si>
   <si>
@@ -288,6 +291,24 @@
     <t xml:space="preserve">#2aa198, #e67e22, #27ae60</t>
   </si>
   <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name - appears in the stats pack Declaration sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jane Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name - appears in the stats pack Declaration sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Research LampPost, Acme Research Partners</t>
+  </si>
+  <si>
     <t xml:space="preserve">Module_Version</t>
   </si>
   <si>
@@ -564,288 +585,276 @@
     <t xml:space="preserve">1000-100000 (more = better design but slower)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mapping_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version_Variable</t>
+    <t xml:space="preserve">Field_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task_Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERSION</t>
   </si>
   <si>
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Column name containing design version number (1, 2, 3...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version, DesignVersion, Block, MD_Version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best_Column_Pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxDiff_T{task}_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pattern for Best choice columns. Use {task} as placeholder for task number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxDiff_T{task}_Best, MD{task}B, Best_{task}, Q5_{task}_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worst_Column_Pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxDiff_T{task}_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pattern for Worst choice columns. Use {task} as placeholder for task number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxDiff_T{task}_Worst, MD{task}W, Worst_{task}, Q5_{task}_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task_Number_Pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{task}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How task number appears in column names (usually just {task})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{task}, T{task}, Task{task}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best_Value_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM_POSITION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What value is stored: ITEM_POSITION (1-5) or ITEM_ID (actual ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM_POSITION (1,2,3,4,5) or ITEM_ID (ITEM_01, ITEM_02...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worst_Value_Type</t>
+    <t xml:space="preserve">Column holding the design version number (1, 2, 3...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST_CHOICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T1_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORST_CHOICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T1_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T2_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T2_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T3_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T3_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T4_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T4_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T5_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T5_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T6_Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best choice for task 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxDiff_T6_Worst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst choice for task 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row per data column. Field_Type is VERSION, BEST_CHOICE or WORST_CHOICE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field_Name must match the column name in your data file exactly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task_Number links each best/worst pair to a DESIGN task; a T1/T2 infix in the name is auto-detected when the column is blank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust the example rows to your own task count and column names.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the cells carry Item_IDs or task positions is set in PROJECT_SETTINGS (Choice_Value_Type).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment_Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment_Def</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include_in_Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age_Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique identifier for the segment group (one ROW per group, not per level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display name in the output tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column in your data file whose LEVELS become the segments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional R expression to derive the grouping (e.g. Age &gt;= 35); blank = use the variable's own values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = include in output (default), 0 = skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- OUTPUT FORMATS ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Design_File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate design file with task assignments (DESIGN mode)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Count_Scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate count-based scores (Best%, Worst%, Net Score)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Aggregate_Logit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fit aggregate multinomial logit model for utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_HB_Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fit Hierarchical Bayes model for individual-level utilities (requires cmdstanr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (requires additional setup)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Segment_Tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate separate score tables for each segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate PNG/PDF visualization charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_HTML_Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate interactive HTML report with SVG charts and tabbed layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (produces self-contained .html file)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Simulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate interactive HTML simulator (head-to-head, portfolio builder)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (requires HB or logit results)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- TURF ANALYSIS ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_TURF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run TURF (Total Unduplicated Reach &amp; Frequency) portfolio optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES or NO (requires individual-level utilities from HB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURF_Max_Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum portfolio size for TURF analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to n_items (default: min(10, n_items))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURF_Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABOVE_MEAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method for classifying items as appealing in TURF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABOVE_MEAN | TOP_3 | TOP_K | ABOVE_ZERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- ANCHORED MAXDIFF ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has_Anchor_Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the survey includes an anchor/must-have question</t>
   </si>
   <si>
     <t xml:space="preserve">Anchor_Variable</t>
   </si>
   <si>
-    <t xml:space="preserve">Column containing anchor/must-have selections (comma-separated Item_IDs or blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MustHave_Items, Anchor_Q (e.g. 'ITEM_01,ITEM_03,ITEM_05')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLUMN PATTERN EXAMPLE:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If your survey has columns: MaxDiff_T1_Best, MaxDiff_T1_Worst, MaxDiff_T2_Best, MaxDiff_T2_Worst, ...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set Best_Column_Pattern = MaxDiff_T{task}_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set Worst_Column_Pattern = MaxDiff_T{task}_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALUE TYPE EXPLANATION:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM_POSITION: Values 1-5 indicate which position in the task was selected (matches design file)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM_ID: Values are the actual Item_IDs (e.g., ITEM_01, ITEM_02) - used when survey stores IDs directly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age_Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouping variable name (e.g., Gender, Age_Group) - segments with same ID are grouped</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display name for this segment level (e.g., Male, Female, 18-34)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column name in your data file containing this variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value to match in the variable (can be numeric or text)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Include in analysis, 0 = Skip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order for display within the segment group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--- OUTPUT FORMATS ---</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Design_File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate design file with task assignments (DESIGN mode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Count_Scores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculate count-based scores (Best%, Worst%, Net Score)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Aggregate_Logit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fit aggregate multinomial logit model for utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_HB_Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fit Hierarchical Bayes model for individual-level utilities (requires cmdstanr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES or NO (requires additional setup)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Segment_Tables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate separate score tables for each segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate PNG/PDF visualization charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_HTML_Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate interactive HTML report with SVG charts and tabbed layout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES or NO (produces self-contained .html file)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Simulator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate interactive HTML simulator (head-to-head, portfolio builder)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES or NO (requires HB or logit results)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Stats_Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--- TURF ANALYSIS ---</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_TURF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run TURF (Total Unduplicated Reach &amp; Frequency) portfolio optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES or NO (requires individual-level utilities from HB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURF_Max_Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum portfolio size for TURF analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 to n_items (default: min(10, n_items))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURF_Threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABOVE_MEAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method for classifying items as appealing in TURF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABOVE_MEAN | TOP_3 | TOP_K | ABOVE_ZERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--- ANCHORED MAXDIFF ---</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has_Anchor_Question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether the survey includes an anchor/must-have question</t>
-  </si>
-  <si>
     <t xml:space="preserve">Column name containing anchor responses (leave blank if Has_Anchor_Question = NO)</t>
   </si>
   <si>
@@ -891,115 +900,46 @@
     <t xml:space="preserve">UTILITY | PREFERENCE_SHARE | BOTH</t>
   </si>
   <si>
-    <t xml:space="preserve">Utility_Scale</t>
+    <t xml:space="preserve">Score_Rescale_Method</t>
   </si>
   <si>
     <t xml:space="preserve">0_100</t>
   </si>
   <si>
-    <t xml:space="preserve">Scale for utility scores: RAW, 0_100, or PROBABILITY</t>
+    <t xml:space="preserve">Scale for utility scores (the setting the engine reads - the old template's Utility_Scale row was silently ignored)</t>
   </si>
   <si>
     <t xml:space="preserve">RAW = logit scale | 0_100 = rescaled 0-100 | PROBABILITY = share of preference</t>
   </si>
   <si>
-    <t xml:space="preserve">Include_Raw_Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include raw response data in output file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include_Diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include model diagnostics and fit statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart_Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart image format: PNG, PDF, or SVG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNG, PDF, SVG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart_Width</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart width in pixels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400-1600 (pixels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart_Height</t>
-  </si>
-  <si>
-    <t xml:space="preserve">600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart height in pixels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300-1200 (pixels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#323367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary brand colour for report theme (hex format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#323367, #1e3a5f, #2c3e50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#CC9900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accent colour for highlights and secondary elements (hex format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#CC9900, #e67e22, #27ae60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Researcher_Logo_Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File path to researcher/agency logo image (PNG/JPG, leave blank for none)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logos/agency_logo.png, C:/Logos/company.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client_Logo_Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File path to client logo image (PNG/JPG, leave blank for none)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logos/client_logo.png, C:/Logos/client_brand.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report_Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom report title (leave blank to use Project_Name from PROJECT_SETTINGS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Preference MaxDiff Study Q1 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include_Methodology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include a methodology section in the HTML report</t>
+    <t xml:space="preserve">Export_Individual_Utils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write the per-respondent utilities sheet (needed for TURF and the tabs export)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min_Respondents_Per_Segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum respondents for a segment to be reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive integer (default 50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output_Item_Sort_Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTILITY_DESC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row order for item tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTILITY_DESC | UTILITY_ASC | ITEM_ID | DISPLAY_ORDER</t>
   </si>
   <si>
     <t xml:space="preserve">Title</t>
@@ -1033,54 +973,6 @@
   </si>
   <si>
     <t xml:space="preserve">Optional file path to an image displayed on the slide (PNG/JPG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images/study_overview.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Figure 1: Study overview and key findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which report panel to embed the image in: summary, preferences, items, turf, segments, diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File path to the image file (PNG/JPG, relative to config or absolute)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional caption text displayed below the image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Preference Study Q1 2026, Product Features MaxDiff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jane Smith, John Doe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research_House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Research LampPost, Acme Research Partners</t>
   </si>
 </sst>
 </file>
@@ -1678,12 +1570,12 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
@@ -1694,12 +1586,12 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
@@ -1718,12 +1610,12 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>22</v>
@@ -1734,12 +1626,12 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>24</v>
@@ -1774,12 +1666,12 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
@@ -1790,12 +1682,12 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>31</v>
@@ -1830,203 +1722,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="50.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="50.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'summary,preferences,items,turf,segments,diagnostics'</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A20</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="75.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>352</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2049,240 +1745,291 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2319,36 +2066,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>1</v>
@@ -2365,13 +2112,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>1</v>
@@ -2388,13 +2135,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>1</v>
@@ -2411,13 +2158,13 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>1</v>
@@ -2434,13 +2181,13 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
@@ -2457,13 +2204,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
@@ -2480,13 +2227,13 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1</v>
@@ -2503,13 +2250,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1</v>
@@ -2526,13 +2273,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>1</v>
@@ -2549,13 +2296,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1</v>
@@ -2572,10 +2319,10 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1</v>
@@ -2583,79 +2330,79 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2679,242 +2426,242 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2964,192 +2711,223 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="100.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="60.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="90.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="110.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>190</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>185</v>
+      <c r="A2" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>189</v>
+      <c r="A3" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>193</v>
+      <c r="A4" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
+      <c r="B6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
+      <c r="A7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>205</v>
+      <c r="A8" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>206</v>
+      <c r="A10" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>207</v>
+      <c r="A11" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>208</v>
+      <c r="A12" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>209</v>
+      <c r="A13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>213</v>
+      <c r="A14" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3166,286 +2944,139 @@
     <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="30.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="80.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>221</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>2</v>
+      <c r="G3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>1</v>
+      <c r="G4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>2</v>
+      <c r="G5" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>3</v>
+      <c r="G6" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="G7" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>236</v>
+      <c r="H7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3467,21 +3098,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>4</v>
@@ -3495,133 +3126,133 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>4</v>
@@ -3635,49 +3266,49 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>4</v>
@@ -3691,63 +3322,63 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>4</v>
@@ -3761,100 +3392,72 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>43</v>
+        <v>300</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>156</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B28" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3862,7 +3465,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="14">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'YES,NO'</xm:f>
@@ -3937,12 +3540,6 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'YES,NO'</xm:f>
-          </x14:formula1>
-          <xm:sqref>B25:B25</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>'ABOVE_MEAN,TOP_3,TOP_K,ABOVE_ZERO'</xm:f>
           </x14:formula1>
           <xm:sqref>B15:B15</xm:sqref>
@@ -3964,155 +3561,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="60.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'YES,NO'</xm:f>
-          </x14:formula1>
-          <xm:sqref>B7:B7</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
     <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
@@ -4121,27 +3569,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>4</v>
@@ -4149,10 +3597,10 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>1</v>
@@ -4160,46 +3608,46 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/modules/maxdiff/templates/maxdiff_config_template.xlsx
+++ b/modules/maxdiff/templates/maxdiff_config_template.xlsx
@@ -3241,7 +3241,7 @@
         <v>260</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>261</v>
